--- a/outputs/Estimated_Losses_ByYear_Municipality_Fire_Road.xlsx
+++ b/outputs/Estimated_Losses_ByYear_Municipality_Fire_Road.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfc708eb55e2c127/Documents/GitHub/JeffersonTownshipTaxResearch/outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="11_BD79460C77E113215CFF31D2F8F2D3C284D99C7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13760469-2EF9-4CB2-916F-CE4F06143C54}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="11_BD79460C77E113215CFF31D2F8F2D3C284D99C7E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9986399D-CF1B-4168-8D99-AC308CA85458}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="24220" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="18">
   <si>
     <t>TaxYear</t>
   </si>
@@ -80,14 +80,23 @@
   <si>
     <t>Estimated Tax Revenue Diverted to TIFs by Jurisdiction and Fund in 000's</t>
   </si>
+  <si>
+    <t>*Road</t>
+  </si>
+  <si>
+    <t>*  - Includes Inside Millage</t>
+  </si>
+  <si>
+    <t>Tax Year</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -134,7 +143,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -242,15 +251,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -478,33 +478,143 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -513,57 +623,96 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="35" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -868,7 +1017,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{305085A5-4FE6-49EA-9E0D-70A3DA05A991}">
-  <dimension ref="A2:K35"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:K37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
@@ -885,50 +1037,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="14"/>
       <c r="H4" s="10"/>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="11"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="3"/>
@@ -1397,641 +1549,650 @@
     </row>
     <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="18"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="21"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="19"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22" s="22"/>
-      <c r="B22" s="33" t="s">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="38"/>
-      <c r="D22" s="33" t="s">
+      <c r="C22" s="22"/>
+      <c r="D22" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="38"/>
-      <c r="F22" s="33" t="s">
+      <c r="E22" s="45"/>
+      <c r="F22" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="33" t="s">
+      <c r="G22" s="46"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J22" s="38"/>
+      <c r="J22" s="45"/>
       <c r="K22" s="23"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23" s="24"/>
-      <c r="B23" s="34" t="s">
+      <c r="A23" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="E23" s="39" t="s">
+      <c r="E23" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="34" t="s">
+      <c r="F23" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" s="39" t="s">
+      <c r="G23" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="34" t="s">
+      <c r="I23" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="J23" s="39" t="s">
+      <c r="J23" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="K23" s="25" t="s">
+      <c r="K23" s="28" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A24" s="26">
+      <c r="A24" s="29">
         <v>2014</v>
       </c>
-      <c r="B24" s="35">
+      <c r="B24" s="30">
         <f>B6/1000</f>
         <v>81.272100224938782</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="31">
         <f t="shared" ref="C24:K24" si="1">C6/1000</f>
         <v>81.272100224938782</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="30">
         <f t="shared" si="1"/>
         <v>45.126551218318625</v>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="31">
         <f t="shared" si="1"/>
         <v>45.126551218318625</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="27">
+      <c r="K24" s="33">
         <f t="shared" si="1"/>
         <v>126.39865144325741</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A25" s="28">
+      <c r="A25" s="34">
         <v>2015</v>
       </c>
-      <c r="B25" s="36">
+      <c r="B25" s="35">
         <f t="shared" ref="B25:K35" si="2">B7/1000</f>
         <v>74.60957627082621</v>
       </c>
-      <c r="C25" s="41">
+      <c r="C25" s="36">
         <f t="shared" si="2"/>
         <v>74.60957627082621</v>
       </c>
-      <c r="D25" s="36">
+      <c r="D25" s="35">
         <f t="shared" si="2"/>
         <v>51.279709357161551</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="36">
         <f t="shared" si="2"/>
         <v>51.279709357161551</v>
       </c>
-      <c r="F25" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="29">
+      <c r="F25" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="38">
         <f t="shared" si="2"/>
         <v>125.88928562798776</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A26" s="26">
+      <c r="A26" s="29">
         <v>2016</v>
       </c>
-      <c r="B26" s="35">
+      <c r="B26" s="30">
         <f t="shared" si="2"/>
         <v>74.27445821626948</v>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="31">
         <f t="shared" si="2"/>
         <v>74.27445821626948</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="30">
         <f t="shared" si="2"/>
         <v>61.019127934732026</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="31">
         <f t="shared" si="2"/>
         <v>61.019127934732026</v>
       </c>
-      <c r="F26" s="35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="27">
+      <c r="F26" s="30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="32">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="33">
         <f t="shared" si="2"/>
         <v>135.29358615100151</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A27" s="28">
+      <c r="A27" s="34">
         <v>2017</v>
       </c>
-      <c r="B27" s="36">
+      <c r="B27" s="35">
         <f t="shared" si="2"/>
         <v>81.230057135438926</v>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="36">
         <f t="shared" si="2"/>
         <v>81.230057135438926</v>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="35">
         <f t="shared" si="2"/>
         <v>67.266529459693061</v>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="36">
         <f t="shared" si="2"/>
         <v>67.266529459693061</v>
       </c>
-      <c r="F27" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="G27" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J27" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K27" s="29">
+      <c r="F27" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G27" s="37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="38">
         <f t="shared" si="2"/>
         <v>148.49658659513199</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A28" s="26">
+      <c r="A28" s="29">
         <v>2018</v>
       </c>
-      <c r="B28" s="35">
+      <c r="B28" s="30">
         <f t="shared" si="2"/>
         <v>80.858472133664293</v>
       </c>
-      <c r="C28" s="40">
+      <c r="C28" s="31">
         <f t="shared" si="2"/>
         <v>80.858472133664293</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="30">
         <f t="shared" si="2"/>
         <v>68.096137358601112</v>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="31">
         <f t="shared" si="2"/>
         <v>68.096137358601112</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="30">
         <f t="shared" si="2"/>
         <v>63.5720909100759</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="32">
         <f t="shared" si="2"/>
         <v>19.482621935014599</v>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="31">
         <f t="shared" si="2"/>
         <v>83.054712845090506</v>
       </c>
-      <c r="I28" s="35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J28" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K28" s="27">
+      <c r="I28" s="30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="33">
         <f t="shared" si="2"/>
         <v>232.00932233735594</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A29" s="28">
+      <c r="A29" s="34">
         <v>2019</v>
       </c>
-      <c r="B29" s="36">
+      <c r="B29" s="35">
         <f t="shared" si="2"/>
         <v>79.47075888534242</v>
       </c>
-      <c r="C29" s="41">
+      <c r="C29" s="36">
         <f t="shared" si="2"/>
         <v>79.47075888534242</v>
       </c>
-      <c r="D29" s="36">
+      <c r="D29" s="35">
         <f t="shared" si="2"/>
         <v>66.909118476188283</v>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="36">
         <f t="shared" si="2"/>
         <v>66.909118476188283</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="35">
         <f t="shared" si="2"/>
         <v>118.162856025038</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="37">
         <f t="shared" si="2"/>
         <v>36.036727078764279</v>
       </c>
-      <c r="H29" s="41">
+      <c r="H29" s="36">
         <f t="shared" si="2"/>
         <v>154.1995831038023</v>
       </c>
-      <c r="I29" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="29">
+      <c r="I29" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="38">
         <f t="shared" si="2"/>
         <v>300.57946046533294</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A30" s="26">
+      <c r="A30" s="29">
         <v>2020</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="30">
         <f t="shared" si="2"/>
         <v>80.180195096880226</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="31">
         <f t="shared" si="2"/>
         <v>80.180195096880226</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="30">
         <f t="shared" si="2"/>
         <v>65.77549402538996</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="31">
         <f t="shared" si="2"/>
         <v>65.77549402538996</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="30">
         <f t="shared" si="2"/>
         <v>156.94080891074302</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="32">
         <f t="shared" si="2"/>
         <v>50.758969752823177</v>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="31">
         <f t="shared" si="2"/>
         <v>207.69977866356618</v>
       </c>
-      <c r="I30" s="35">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J30" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K30" s="27">
+      <c r="I30" s="30">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="31">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="33">
         <f t="shared" si="2"/>
         <v>353.65546778583638</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A31" s="28">
+      <c r="A31" s="34">
         <v>2021</v>
       </c>
-      <c r="B31" s="36">
+      <c r="B31" s="35">
         <f t="shared" si="2"/>
         <v>79.255347944302713</v>
       </c>
-      <c r="C31" s="41">
+      <c r="C31" s="36">
         <f t="shared" si="2"/>
         <v>79.255347944302713</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="35">
         <f t="shared" si="2"/>
         <v>64.830280477867532</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="36">
         <f t="shared" si="2"/>
         <v>64.830280477867532</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="35">
         <f t="shared" si="2"/>
         <v>263.86840534490779</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="37">
         <f t="shared" si="2"/>
         <v>81.98189112863426</v>
       </c>
-      <c r="H31" s="41">
+      <c r="H31" s="36">
         <f t="shared" si="2"/>
         <v>345.85029647354207</v>
       </c>
-      <c r="I31" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="29">
+      <c r="I31" s="35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="38">
         <f t="shared" si="2"/>
         <v>489.93592489571228</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A32" s="26">
+      <c r="A32" s="29">
         <v>2022</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="30">
         <f t="shared" si="2"/>
         <v>99.305809668307134</v>
       </c>
-      <c r="C32" s="40">
+      <c r="C32" s="31">
         <f t="shared" si="2"/>
         <v>99.305809668307134</v>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="30">
         <f t="shared" si="2"/>
         <v>81.417737077101322</v>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="31">
         <f t="shared" si="2"/>
         <v>81.417737077101322</v>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="30">
         <f t="shared" si="2"/>
         <v>475.9338613655795</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="32">
         <f t="shared" si="2"/>
         <v>121.9694173127983</v>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="31">
         <f t="shared" si="2"/>
         <v>597.90327867837777</v>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="30">
         <f t="shared" si="2"/>
         <v>22.380729606112929</v>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="31">
         <f t="shared" si="2"/>
         <v>22.380729606112929</v>
       </c>
-      <c r="K32" s="27">
+      <c r="K32" s="33">
         <f t="shared" si="2"/>
         <v>801.00755502989909</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A33" s="28">
+      <c r="A33" s="34">
         <v>2023</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="35">
         <f t="shared" si="2"/>
         <v>100.10673012623039</v>
       </c>
-      <c r="C33" s="41">
+      <c r="C33" s="36">
         <f t="shared" si="2"/>
         <v>100.10673012623039</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="35">
         <f t="shared" si="2"/>
         <v>64.3020158518774</v>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="36">
         <f t="shared" si="2"/>
         <v>64.3020158518774</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="35">
         <f t="shared" si="2"/>
         <v>566.09247936077145</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G33" s="37">
         <f t="shared" si="2"/>
         <v>148.8327422078589</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="36">
         <f t="shared" si="2"/>
         <v>714.92522156863026</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="35">
         <f t="shared" si="2"/>
         <v>72.92302135552967</v>
       </c>
-      <c r="J33" s="41">
+      <c r="J33" s="36">
         <f t="shared" si="2"/>
         <v>72.92302135552967</v>
       </c>
-      <c r="K33" s="29">
+      <c r="K33" s="38">
         <f t="shared" si="2"/>
         <v>952.25698890226772</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A34" s="26">
+      <c r="A34" s="29">
         <v>2024</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="30">
         <f t="shared" si="2"/>
         <v>99.621148629688165</v>
       </c>
-      <c r="C34" s="40">
+      <c r="C34" s="31">
         <f t="shared" si="2"/>
         <v>99.621148629688165</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="30">
         <f t="shared" si="2"/>
         <v>64.195415771812634</v>
       </c>
-      <c r="E34" s="40">
+      <c r="E34" s="31">
         <f t="shared" si="2"/>
         <v>64.195415771812634</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="30">
         <f t="shared" si="2"/>
         <v>593.08816115580066</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="32">
         <f t="shared" si="2"/>
         <v>159.60205384588468</v>
       </c>
-      <c r="H34" s="40">
+      <c r="H34" s="31">
         <f t="shared" si="2"/>
         <v>752.69021500168526</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="30">
         <f t="shared" si="2"/>
         <v>71.840469589731896</v>
       </c>
-      <c r="J34" s="40">
+      <c r="J34" s="31">
         <f t="shared" si="2"/>
         <v>71.840469589731896</v>
       </c>
-      <c r="K34" s="27">
+      <c r="K34" s="33">
         <f t="shared" si="2"/>
         <v>988.34724899291803</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="40">
         <f t="shared" si="2"/>
         <v>930.18465433188862</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="41">
         <f t="shared" si="2"/>
         <v>930.18465433188862</v>
       </c>
-      <c r="D35" s="37">
+      <c r="D35" s="40">
         <f t="shared" si="2"/>
         <v>700.21811700874355</v>
       </c>
-      <c r="E35" s="42">
+      <c r="E35" s="41">
         <f t="shared" si="2"/>
         <v>700.21811700874355</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="40">
         <f t="shared" si="2"/>
         <v>2237.6586630729166</v>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="42">
         <f t="shared" si="2"/>
         <v>618.66442326177821</v>
       </c>
-      <c r="H35" s="42">
+      <c r="H35" s="41">
         <f t="shared" si="2"/>
         <v>2856.3230863346944</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="40">
         <f t="shared" si="2"/>
         <v>201.30945980415794</v>
       </c>
-      <c r="J35" s="42">
+      <c r="J35" s="41">
         <f t="shared" si="2"/>
         <v>201.30945980415794</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="43">
         <f t="shared" si="2"/>
         <v>4688.0353174794845</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="A2:J3"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="A20:K21"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="A2:J3"/>
   </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="66" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
